--- a/data_lake/descensos_temperatura/dt=2026-07-30/excel/PronosticoMunicipal_DescensosTemperatura_72h.xlsx
+++ b/data_lake/descensos_temperatura/dt=2026-07-30/excel/PronosticoMunicipal_DescensosTemperatura_72h.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,17 +488,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -506,12 +506,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>52573</t>
+          <t>52317</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Puerres</t>
+          <t>Guachucal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,17 +541,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -559,12 +559,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>52317</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Guachucal</t>
+          <t>Cumbal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -594,17 +594,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -612,12 +612,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>52287</t>
+          <t>52720</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Funes</t>
+          <t>Sapuyes</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -647,17 +647,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -665,12 +665,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>52227</t>
+          <t>52435</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Cumbal</t>
+          <t>Mallama</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -679,11 +679,11 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -700,17 +700,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -718,17 +718,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>19743</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sapuyes</t>
+          <t>Silvia</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -753,17 +753,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -771,17 +771,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>52788</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tangua</t>
+          <t>Jambaló</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -806,17 +806,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -824,17 +824,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>19517</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pasto</t>
+          <t>Páez</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -859,17 +859,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -877,17 +877,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>52435</t>
+          <t>19821</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Mallama</t>
+          <t>Toribío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -912,17 +912,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -930,17 +930,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>50370</t>
+          <t>73616</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Uribe</t>
+          <t>Rioblanco</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -965,17 +965,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -983,12 +983,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>50370</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Cubarral</t>
+          <t>Uribe</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>50400</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Santa Isabel</t>
+          <t>Lejanías</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1089,17 +1089,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>73461</t>
+          <t>41206</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Murillo</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1142,17 +1142,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>50223</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Villamaria</t>
+          <t>Cubarral</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1195,17 +1195,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>73870</t>
+          <t>25120</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Villahermosa</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1230,17 +1230,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1248,17 +1248,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>68318</t>
+          <t>73168</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Guaca</t>
+          <t>Chaparral</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1283,17 +1283,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>68705</t>
+          <t>50318</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
+          <t>Guamal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1354,17 +1354,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>54174</t>
+          <t>76834</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Chitagá</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Norte de Santander</t>
+          <t>Valle del Cauca</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1389,17 +1389,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1407,17 +1407,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>54743</t>
+          <t>50006</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Silos</t>
+          <t>Acacías</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Norte de Santander</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>52317</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Guachucal</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>52227</t>
+          <t>73622</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Cumbal</t>
+          <t>Roncesvalles</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1566,17 +1566,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>41801</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Teruel</t>
+          <t>Gutiérrez</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1619,17 +1619,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>19517</t>
+          <t>63302</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Páez</t>
+          <t>Génova</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Quindío</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>19821</t>
+          <t>76736</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Toribío</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Valle del Cauca</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -1725,17 +1725,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>73555</t>
+          <t>25845</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Planadas</t>
+          <t>Une</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1778,17 +1778,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>50370</t>
+          <t>25178</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Uribe</t>
+          <t>Chipaque</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -1831,25 +1831,25 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>50400</t>
+          <t>25754</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Lejanías</t>
+          <t>Soacha</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1884,17 +1884,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>73686</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Cubarral</t>
+          <t>Santa Isabel</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>50318</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Guamal</t>
+          <t>Bogotá, D.C.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -1990,17 +1990,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>73461</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Gutiérrez</t>
+          <t>Murillo</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2043,17 +2043,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>25845</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Une</t>
+          <t>Villamaria</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>73870</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bogotá, D.C.</t>
+          <t>Villahermosa</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Aquitania</t>
+          <t>Monguí</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Monguí</t>
+          <t>Sogamoso</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>15464</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sogamoso</t>
+          <t>Mongua</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Mongua</t>
+          <t>Tópaga</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>15820</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tópaga</t>
+          <t>Gámeza</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>15790</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Gámeza</t>
+          <t>Tasco</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Corrales</t>
+          <t>Cerinza</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>15790</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tasco</t>
+          <t>Santa Rosa De Viterbo</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Cerinza</t>
+          <t>Duitama</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>15757</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Santa Rosa De Viterbo</t>
+          <t>Socha</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>15087</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Duitama</t>
+          <t>Belén</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>15757</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Socha</t>
+          <t>Socotá</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>15839</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Belén</t>
+          <t>Tutazá</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2838,17 +2838,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>68264</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Socotá</t>
+          <t>Encino</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>15183</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tutazá</t>
+          <t>Chita</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>68264</t>
+          <t>85136</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Encino</t>
+          <t>La Salina</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Casanare</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -2997,12 +2997,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>15183</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Chita</t>
+          <t>El Cocuy</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3050,25 +3050,25 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>85136</t>
+          <t>81794</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>La Salina</t>
+          <t>Tame</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Casanare</t>
+          <t>Arauca</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3103,17 +3103,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>68217</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Coromoro</t>
+          <t>Güicán De La Sierra</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>El Cocuy</t>
+          <t>Chiscas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3170,11 +3170,11 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3191,17 +3191,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-30 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-07-31 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3209,17 +3209,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>68502</t>
+          <t>52560</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Onzaga</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -3244,17 +3244,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-30 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-07-31 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -3262,17 +3262,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>52215</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>El Espino</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -3297,17 +3297,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-30 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-07-31 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -3315,25 +3315,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>81794</t>
+          <t>52356</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tame</t>
+          <t>Ipiales</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Arauca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3350,17 +3350,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-30 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-31 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -3368,25 +3368,25 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>15332</t>
+          <t>52224</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Güicán De La Sierra</t>
+          <t>Cuaspud</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3403,17 +3403,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-30 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-31 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3421,25 +3421,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>15180</t>
+          <t>52573</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Chiscas</t>
+          <t>Puerres</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>52560</t>
+          <t>52022</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Aldana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3488,11 +3488,11 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3527,12 +3527,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>52356</t>
+          <t>52585</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Ipiales</t>
+          <t>Pupiales</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3541,11 +3541,11 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3580,12 +3580,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>52224</t>
+          <t>52317</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Cuaspud</t>
+          <t>Guachucal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>52573</t>
+          <t>52287</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Puerres</t>
+          <t>Funes</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>52022</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Aldana</t>
+          <t>Cumbal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>52720</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Pupiales</t>
+          <t>Sapuyes</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3753,11 +3753,11 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3792,12 +3792,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>52317</t>
+          <t>52788</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Guachucal</t>
+          <t>Tangua</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>52287</t>
+          <t>52838</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Funes</t>
+          <t>Túquerres</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>52227</t>
+          <t>52001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Cumbal</t>
+          <t>Pasto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3912,11 +3912,11 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3951,12 +3951,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>52435</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Sapuyes</t>
+          <t>Mallama</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4004,17 +4004,17 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>52788</t>
+          <t>19701</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tangua</t>
+          <t>Santa Rosa</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -4057,25 +4057,25 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>52838</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Túquerres</t>
+          <t>San Sebastián</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -4110,17 +4110,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>19397</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Pasto</t>
+          <t>La Vega</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -4163,17 +4163,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>52435</t>
+          <t>41668</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Mallama</t>
+          <t>San Agustín</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -4216,17 +4216,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>52378</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>La Cruz</t>
+          <t>Saladoblanco</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4269,17 +4269,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>41359</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Santa Rosa</t>
+          <t>Isnos</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4322,17 +4322,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>41378</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>San Sebastián</t>
+          <t>La Argentina</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -4375,17 +4375,17 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>19397</t>
+          <t>00000</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>La Vega</t>
+          <t>Area En Litigio Cauca - Huila</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>41668</t>
+          <t>19760</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>San Agustín</t>
+          <t>Sotará</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>19585</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Saladoblanco</t>
+          <t>Puracé</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -4534,17 +4534,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>41359</t>
+          <t>19824</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Isnos</t>
+          <t>Totoró</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>19355</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>La Argentina</t>
+          <t>Inzá</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -4640,17 +4640,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>00000</t>
+          <t>19743</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Area En Litigio Cauca - Huila</t>
+          <t>Silvia</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -4693,25 +4693,25 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>19760</t>
+          <t>41801</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sotará</t>
+          <t>Teruel</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -4746,12 +4746,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Puracé</t>
+          <t>Jambaló</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>19824</t>
+          <t>19517</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Totoró</t>
+          <t>Páez</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4813,11 +4813,11 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>19821</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Inzá</t>
+          <t>Toribío</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4866,11 +4866,11 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -4905,12 +4905,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>19212</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Silvia</t>
+          <t>Corinto</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4958,25 +4958,25 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>41801</t>
+          <t>73555</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Teruel</t>
+          <t>Planadas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -5011,17 +5011,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>19364</t>
+          <t>73616</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Jambaló</t>
+          <t>Rioblanco</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -5064,17 +5064,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>19517</t>
+          <t>50370</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Páez</t>
+          <t>Uribe</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -5117,17 +5117,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>19821</t>
+          <t>50400</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Toribío</t>
+          <t>Lejanías</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -5170,17 +5170,17 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>19212</t>
+          <t>41206</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Corinto</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -5223,25 +5223,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>73555</t>
+          <t>50223</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Planadas</t>
+          <t>Cubarral</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -5276,17 +5276,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>73616</t>
+          <t>25120</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Rioblanco</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -5329,17 +5329,17 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>50370</t>
+          <t>73168</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Uribe</t>
+          <t>Chaparral</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>50400</t>
+          <t>50318</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Lejanías</t>
+          <t>Guamal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5435,17 +5435,17 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>41206</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -5488,17 +5488,17 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>76111</t>
+          <t>73622</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Roncesvalles</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -5541,17 +5541,17 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Cubarral</t>
+          <t>Gutiérrez</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -5594,17 +5594,17 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>63302</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Génova</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Quindío</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -5647,17 +5647,17 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>73168</t>
+          <t>25845</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Chaparral</t>
+          <t>Une</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -5700,17 +5700,17 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>50318</t>
+          <t>25178</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Guamal</t>
+          <t>Chipaque</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -5753,17 +5753,17 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>76834</t>
+          <t>73001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>Ibagué</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -5806,17 +5806,17 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>25649</t>
+          <t>73043</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>Anzoátegui</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -5859,25 +5859,25 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>73622</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Roncesvalles</t>
+          <t>Bogotá, D.C.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -5912,17 +5912,17 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>25053</t>
+          <t>66682</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Arbeláez</t>
+          <t>Santa Rosa De Cabal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -5965,17 +5965,17 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Gutiérrez</t>
+          <t>Villamaria</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -6018,17 +6018,17 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>63302</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Génova</t>
+          <t>Gámeza</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Quindío</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -6071,17 +6071,17 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>15790</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Pasca</t>
+          <t>Tasco</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -6124,17 +6124,17 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>76736</t>
+          <t>15757</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Socha</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -6177,17 +6177,17 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>25845</t>
+          <t>85136</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Une</t>
+          <t>La Salina</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Casanare</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -6230,17 +6230,17 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>25178</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Chipaque</t>
+          <t>El Cocuy</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -6283,17 +6283,17 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>73001</t>
+          <t>81794</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Ibagué</t>
+          <t>Tame</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Arauca</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -6336,17 +6336,17 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>73043</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Anzoátegui</t>
+          <t>Güicán De La Sierra</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -6389,17 +6389,17 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Santa Isabel</t>
+          <t>Chiscas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -6424,17 +6424,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -6442,17 +6442,17 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>52224</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Bogotá, D.C.</t>
+          <t>Cuaspud</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -6477,17 +6477,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -6495,17 +6495,17 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>73461</t>
+          <t>52573</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Murillo</t>
+          <t>Puerres</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -6530,17 +6530,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -6548,17 +6548,17 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>73870</t>
+          <t>52022</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Villahermosa</t>
+          <t>Aldana</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>81794</t>
+          <t>52585</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Tame</t>
+          <t>Pupiales</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Arauca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -6654,17 +6654,17 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>15332</t>
+          <t>52317</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Güicán De La Sierra</t>
+          <t>Guachucal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -6689,17 +6689,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -6707,23 +6707,4899 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
+          <t>52287</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Funes</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>3</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>12</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>52227</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Cumbal</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>3</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>12</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>52720</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sapuyes</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>3</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>12</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>52788</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Tangua</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>3</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>12</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>52838</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Túquerres</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>3</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>12</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>52001</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>3</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>12</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>52435</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Mallama</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>3</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>12</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>52378</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>La Cruz</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>3</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>12</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>19701</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Santa Rosa</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>3</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>12</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>19693</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>San Sebastián</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>3</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>12</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>19397</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>La Vega</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>3</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>12</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>41668</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>San Agustín</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>3</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>12</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Saladoblanco</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>3</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>12</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>41359</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Isnos</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>3</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>12</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>41378</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>La Argentina</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>3</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>12</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>00000</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Area En Litigio Cauca - Huila</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>3</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>12</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>19760</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sotará</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>3</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>12</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>19585</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Puracé</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>3</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>12</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>19824</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Totoró</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>3</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>12</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>19355</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Inzá</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>3</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>12</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>19743</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Silvia</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>3</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>12</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>41801</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Teruel</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>3</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>12</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>19364</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Jambaló</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>3</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>12</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>19517</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Páez</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>3</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>12</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>19821</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Toribío</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>3</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>12</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>19212</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Corinto</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>3</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>12</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>73555</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Planadas</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>3</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>12</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>73616</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Rioblanco</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>3</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>12</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>50370</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Uribe</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>3</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>12</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>50400</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Lejanías</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>3</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>12</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>41206</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>3</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>12</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>76111</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Buga</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>3</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>12</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>50223</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Cubarral</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>4</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>12</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>25120</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Cabrera</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>3</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>12</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>73168</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Chaparral</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>3</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>12</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>50318</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Guamal</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>4</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>12</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>76834</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Tuluá</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>3</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>12</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>25649</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>4</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>12</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>73622</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Roncesvalles</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>3</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>12</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>25053</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Arbeláez</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>3</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>12</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>25339</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Gutiérrez</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>4</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>12</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>63302</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Génova</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>3</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>12</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>25535</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Pasca</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>3</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>12</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>76736</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>3</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>12</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>25845</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Une</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>3</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>12</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>25178</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Chipaque</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>3</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>12</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>25754</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Soacha</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>3</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>12</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>73001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>3</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>12</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>63690</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Salento</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>3</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>12</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>73043</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Anzoátegui</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>3</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>12</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>73686</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Santa Isabel</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>3</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>12</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>25377</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>La Calera</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>3</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>12</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>11001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>4</v>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>12</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>66001</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>3</v>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>12</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>73461</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Murillo</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>3</v>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>12</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>25322</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Guasca</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>3</v>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>12</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>66682</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Santa Rosa De Cabal</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>3</v>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>12</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>17873</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Villamaria</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>3</v>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>12</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>73870</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Villahermosa</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>3</v>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>12</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>73152</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Casabianca</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>3</v>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>12</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>73347</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Herveo</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>3</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>12</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>15822</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Tota</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>3</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>12</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>15226</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Cuítiva</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>3</v>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>12</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>15047</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Aquitania</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>3</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>12</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>15362</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Iza</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>3</v>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>12</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>15466</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Monguí</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>3</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>12</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>15759</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sogamoso</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>3</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>12</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>15464</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Mongua</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>3</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>12</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>15820</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Tópaga</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>3</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>12</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>15296</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Gámeza</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>3</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>12</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>15215</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Corrales</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>3</v>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>12</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>15790</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Tasco</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>3</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>12</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>15162</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Cerinza</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J191" t="n">
+        <v>3</v>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>12</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>15693</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Santa Rosa De Viterbo</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J192" t="n">
+        <v>3</v>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>12</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>15238</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Duitama</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J193" t="n">
+        <v>3</v>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>12</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>15757</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Socha</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
+        <v>3</v>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>12</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>15087</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Belén</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J195" t="n">
+        <v>3</v>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>12</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>15755</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Socotá</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J196" t="n">
+        <v>3</v>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>12</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>15839</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Tutazá</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J197" t="n">
+        <v>3</v>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>12</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>68264</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Encino</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>3</v>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>12</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>15183</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Chita</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>3</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>12</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>85136</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>La Salina</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>4</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>12</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>68217</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Coromoro</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>3</v>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>12</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>15244</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>El Cocuy</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>4</v>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>12</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>15673</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>San Mateo</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>3</v>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>12</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>15317</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Guacamayas</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J204" t="n">
+        <v>3</v>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>12</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>15522</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Panqueba</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J205" t="n">
+        <v>3</v>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>12</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>68502</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Onzaga</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="J206" t="n">
+        <v>3</v>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>12</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>15248</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>El Espino</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J207" t="n">
+        <v>3</v>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>12</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>81794</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Tame</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="J208" t="n">
+        <v>4</v>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>12</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>15332</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Güicán De La Sierra</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J209" t="n">
+        <v>4</v>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>12</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
           <t>15180</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="H210" t="inlineStr">
         <is>
           <t>Chiscas</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="I210" t="inlineStr">
         <is>
           <t>Boyacá</t>
         </is>
       </c>
-      <c r="J119" t="n">
-        <v>3</v>
-      </c>
-      <c r="K119" t="inlineStr">
+      <c r="J210" t="n">
+        <v>4</v>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:00</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:00</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>12</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>81300</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Fortul</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="J211" t="n">
+        <v>3</v>
+      </c>
+      <c r="K211" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
